--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486865_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486865_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8946</v>
+        <v>4.5876</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8809</v>
+        <v>1.4039</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0136</v>
+        <v>3.1836</v>
       </c>
       <c r="G2" t="n">
         <v>2.5887</v>
@@ -610,13 +610,13 @@
         <v>3.2855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6015</v>
+        <v>0.2945</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0854</v>
+        <v>0.4376</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6868</v>
+        <v>-0.1431</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3491</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4009</v>
+        <v>4.479</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0072</v>
+        <v>3.7592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3937</v>
+        <v>0.7198</v>
       </c>
       <c r="G3" t="n">
         <v>5.0488</v>
@@ -688,13 +688,13 @@
         <v>3.4908</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3523</v>
+        <v>-0.2742</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4066</v>
+        <v>0.1587</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7589</v>
+        <v>-0.4328</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5277</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8724</v>
+        <v>4.0868</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8673</v>
+        <v>2.1817</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0051</v>
+        <v>1.9051</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9088000000000001</v>
+        <v>1.6188</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2456</v>
+        <v>0.6165</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3368</v>
+        <v>1.0024</v>
       </c>
       <c r="J4" t="n">
-        <v>2.65</v>
+        <v>2.0734</v>
       </c>
       <c r="K4" t="n">
-        <v>1.966</v>
+        <v>0.8633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7412</v>
+        <v>-0.4545</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7204</v>
+        <v>-0.2468</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0208</v>
+        <v>-0.2077</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0534</v>
+        <v>2.6694</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4641</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5611</v>
+        <v>-0.2015</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0386</v>
+        <v>0.1084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5224</v>
+        <v>-0.3098</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2748</v>
+        <v>3.412</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4882</v>
+        <v>2.7627</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7865</v>
+        <v>0.6494</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6188</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6165</v>
+        <v>1.2456</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0024</v>
+        <v>-0.3368</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0734</v>
+        <v>2.65</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8633</v>
+        <v>1.966</v>
       </c>
       <c r="L5" t="n">
-        <v>1.21</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4545</v>
+        <v>-1.7412</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2468</v>
+        <v>-0.7204</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2077</v>
+        <v>-1.0208</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6694</v>
+        <v>2.4641</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0135</v>
+        <v>0.1007</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5851</v>
+        <v>-0.066</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4284</v>
+        <v>0.1667</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3858</v>
+        <v>3.3335</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0439</v>
+        <v>1.7555</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3418</v>
+        <v>1.578</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7269</v>
+        <v>1.456</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3797</v>
+        <v>-0.3016</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3472</v>
+        <v>1.7576</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8473</v>
+        <v>3.3627</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5713</v>
+        <v>0.8633</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2759</v>
+        <v>2.4994</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1204</v>
+        <v>-1.9068</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1917</v>
+        <v>-1.1649</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0713</v>
+        <v>-0.7418</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-2.4641</v>
       </c>
       <c r="R6" t="n">
         <v>2.6694</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8929</v>
+        <v>-0.9028</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4411</v>
+        <v>-0.3217</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5481</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8768</v>
+        <v>2.575</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2177</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6591</v>
+        <v>1.3963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2982</v>
+        <v>1.8289</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9574</v>
+        <v>1.3389</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3408</v>
+        <v>0.49</v>
       </c>
       <c r="G7" t="n">
-        <v>1.456</v>
+        <v>1.7269</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3016</v>
+        <v>0.3797</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7576</v>
+        <v>1.3472</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3627</v>
+        <v>1.8473</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8633</v>
+        <v>0.5713</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4994</v>
+        <v>1.2759</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9068</v>
+        <v>-0.1204</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1649</v>
+        <v>-0.1917</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7418</v>
+        <v>0.0713</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4641</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
         <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.938</v>
+        <v>0.3361</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1198</v>
+        <v>0.736</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8182</v>
+        <v>-0.3999</v>
       </c>
       <c r="V7" t="n">
-        <v>2.575</v>
+        <v>-1.8768</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>-0.2177</v>
       </c>
       <c r="X7" t="n">
-        <v>1.3963</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9629</v>
+        <v>1.0822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5805</v>
+        <v>2.2659</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3825</v>
+        <v>-1.1837</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7561</v>
+        <v>-1.9317</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7485</v>
+        <v>-1.9106</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.0211</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7739</v>
+        <v>0.2225</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0244</v>
+        <v>-0.3825</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2506</v>
+        <v>0.605</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0177</v>
+        <v>-2.1543</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2759</v>
+        <v>-1.5282</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7418</v>
+        <v>-0.6261</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>3.6962</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0999</v>
+        <v>-0.5754</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0386</v>
+        <v>-0.1086</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0613</v>
+        <v>-0.4668</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3573</v>
+        <v>2.3573</v>
       </c>
       <c r="W8" t="n">
+        <v>2.3573</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.3573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6572</v>
+        <v>1.0082</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7816</v>
+        <v>0.6851</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1244</v>
+        <v>0.3232</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9317</v>
+        <v>0.7561</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9106</v>
+        <v>1.7485</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0211</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2225</v>
+        <v>1.7739</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3825</v>
+        <v>2.0244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.605</v>
+        <v>-0.2506</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1543</v>
+        <v>-1.0177</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5282</v>
+        <v>-0.2759</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6261</v>
+        <v>-0.7418</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>3.6962</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0004</v>
+        <v>0.1453</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5928</v>
+        <v>0.1432</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4075</v>
+        <v>0.002</v>
       </c>
       <c r="V9" t="n">
-        <v>2.3573</v>
+        <v>-2.3573</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>P. LLORACH CORNELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9984</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0028</v>
+        <v>-1.215</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9956</v>
+        <v>0.3777</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9274</v>
+        <v>0.1255</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.301</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3736</v>
+        <v>0.213</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0245</v>
+        <v>-0.4323</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5806</v>
+        <v>-0.3664</v>
       </c>
       <c r="L10" t="n">
-        <v>0.605</v>
+        <v>-0.0659</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9519</v>
+        <v>0.5579</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7204</v>
+        <v>0.2789</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2314</v>
+        <v>0.2789</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2414</v>
+        <v>0.0639</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1781</v>
+        <v>0.2441</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4196</v>
+        <v>-0.1801</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. LLORACH CORNELLES</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0011</v>
+        <v>-0.9342</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3196</v>
+        <v>-0.1461</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3185</v>
+        <v>-0.7881</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1255</v>
+        <v>-0.9274</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-1.301</v>
       </c>
       <c r="I11" t="n">
-        <v>0.213</v>
+        <v>0.3736</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4323</v>
+        <v>0.0245</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3664</v>
+        <v>-0.5806</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0659</v>
+        <v>0.605</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5579</v>
+        <v>-0.9519</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2789</v>
+        <v>-0.7204</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2789</v>
+        <v>-0.2314</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0999</v>
+        <v>-0.1773</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1395</v>
+        <v>0.0348</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2394</v>
+        <v>-0.2121</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.42</v>
+        <v>-2.4835</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2297</v>
+        <v>-1.4118</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1904</v>
+        <v>-1.0718</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1848</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1613</v>
+        <v>-0.2248</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0386</v>
+        <v>-0.1434</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4579</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0857</v>
+        <v>-3.6631</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03</v>
+        <v>-0.6964</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0557</v>
+        <v>-2.9668</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0317</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7139</v>
+        <v>0.1365</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9336</v>
+        <v>0.2673</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7679</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.2416</v>
+        <v>15.9002</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0249</v>
+        <v>12.6836</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2164</v>
+        <v>3.216400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>8.154</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6557</v>
+        <v>1.655699999999999</v>
       </c>
       <c r="I14" t="n">
         <v>6.498400000000001</v>
@@ -1546,13 +1546,13 @@
         <v>25.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9375</v>
+        <v>-1.279</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8316000000000002</v>
+        <v>1.4904</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7692</v>
+        <v>-2.769</v>
       </c>
       <c r="V14" t="n">
         <v>-3.2955</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0754</v>
+        <v>2.4181</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7788</v>
+        <v>2.1511</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2966</v>
+        <v>0.267</v>
       </c>
       <c r="G15" t="n">
         <v>2.4563</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9334</v>
+        <v>0.2761</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2939</v>
+        <v>0.6662</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3605</v>
+        <v>-0.3902</v>
       </c>
       <c r="V15" t="n">
         <v>5.0246</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0082</v>
+        <v>2.2907</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3486</v>
+        <v>-0.244</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3568</v>
+        <v>2.5347</v>
       </c>
       <c r="G16" t="n">
         <v>1.2574</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0527</v>
+        <v>0.3352</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0077</v>
+        <v>0.1123</v>
       </c>
       <c r="U16" t="n">
-        <v>0.045</v>
+        <v>0.2228</v>
       </c>
       <c r="V16" t="n">
         <v>0.6982</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7941</v>
+        <v>1.531</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7981</v>
+        <v>2.9705</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.004</v>
+        <v>-1.4396</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8612</v>
+        <v>0.0832</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3977</v>
+        <v>1.3461</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5365</v>
+        <v>-1.2629</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0914</v>
+        <v>1.1294</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4469</v>
+        <v>1.8137</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6445</v>
+        <v>-0.6843</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2302</v>
+        <v>-1.0462</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0492</v>
+        <v>-0.4676</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.181</v>
+        <v>-0.5786</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2855</v>
+        <v>-0.2053</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6762</v>
+        <v>-0.1559</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1626</v>
+        <v>-0.0931</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8994</v>
+        <v>0.3716</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8295</v>
+        <v>2.1396</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0698</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7063</v>
+        <v>1.0643</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5521</v>
+        <v>1.2165</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8458</v>
+        <v>-0.1523</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0832</v>
+        <v>0.8612</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3461</v>
+        <v>2.3977</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2629</v>
+        <v>-1.5365</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1294</v>
+        <v>3.0914</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8137</v>
+        <v>2.4469</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6843</v>
+        <v>0.6445</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0462</v>
+        <v>-2.2302</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4676</v>
+        <v>-0.0492</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5786</v>
+        <v>-2.181</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-3.2855</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9806</v>
+        <v>0.9464</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5115</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4691</v>
+        <v>0.3653</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3716</v>
+        <v>0.8994</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1396</v>
+        <v>0.8295</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7679</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5583</v>
+        <v>-1.499</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9088000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6495</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.637</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3877</v>
+        <v>-2.4731</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0395</v>
+        <v>-1.3533</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3482</v>
+        <v>-1.1198</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1309</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.1656</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.2673</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6612</v>
+        <v>-0.4328</v>
       </c>
       <c r="V20" t="n">
         <v>1.8768</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1803</v>
+        <v>-2.7837</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7426</v>
+        <v>-0.9333</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4378</v>
+        <v>-1.8504</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4124</v>
+        <v>-2.3442</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2268</v>
+        <v>0.6422</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6392</v>
+        <v>-2.9864</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1602</v>
+        <v>0.2415</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7786</v>
+        <v>1.5573</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-1.3158</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5726</v>
+        <v>-2.5857</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.9151</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0208</v>
+        <v>-1.6706</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5545</v>
+        <v>0.2237</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1163</v>
+        <v>0.5501</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6708</v>
+        <v>-0.3263</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.117</v>
+        <v>-0.8686</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2402</v>
+        <v>-0.6982</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>-0.1704</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2666</v>
+        <v>-2.9415</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2471</v>
+        <v>-0.5334</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0195</v>
+        <v>-2.4081</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3442</v>
+        <v>-1.4124</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6422</v>
+        <v>0.2268</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.9864</v>
+        <v>-1.6392</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2415</v>
+        <v>0.1602</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5573</v>
+        <v>0.7786</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3158</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5857</v>
+        <v>-1.5726</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9151</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6706</v>
+        <v>-1.0208</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2592</v>
+        <v>0.7933</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2362</v>
+        <v>0.0929</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4954</v>
+        <v>0.7004</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8686</v>
+        <v>-2.117</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1704</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3094</v>
+        <v>-3.3966</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6837</v>
+        <v>-1.4745</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6257</v>
+        <v>-1.9221</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4254</v>
@@ -2248,13 +2248,13 @@
         <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1858</v>
+        <v>-0.273</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4457</v>
+        <v>-0.2364</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2598</v>
+        <v>-0.0366</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2874</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.538</v>
+        <v>-3.9669</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.857</v>
+        <v>-2.4846</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.681</v>
+        <v>-1.4822</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2327</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0971</v>
+        <v>0.6683</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2357</v>
+        <v>0.6081</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1386</v>
+        <v>0.0602</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1704</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.585</v>
+        <v>-4.7873</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5181</v>
+        <v>-1.6227</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0669</v>
+        <v>-3.1646</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6296</v>
@@ -2404,13 +2404,13 @@
         <v>1.2321</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2294</v>
+        <v>0.0271</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3253</v>
+        <v>0.2207</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0959</v>
+        <v>-0.1936</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1314</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.2413</v>
+        <v>-14.544</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.2164</v>
+        <v>-3.216500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.025</v>
+        <v>-11.3276</v>
       </c>
       <c r="G26" t="n">
         <v>-8.1541</v>
@@ -2482,13 +2482,13 @@
         <v>13.3473</v>
       </c>
       <c r="S26" t="n">
-        <v>1.9376</v>
+        <v>2.6349</v>
       </c>
       <c r="T26" t="n">
-        <v>2.769</v>
+        <v>2.7692</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8314000000000002</v>
+        <v>-0.1343</v>
       </c>
       <c r="V26" t="n">
         <v>3.295800000000001</v>
